--- a/Momentum_Paper_Trading_Journal.xlsx
+++ b/Momentum_Paper_Trading_Journal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeneshKumarPatwa\Documents\Cloude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50437F9E-16B6-4F2C-BA9E-4B12F4D6D0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5269B6D-0A92-409B-ACFF-84398AF221F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{DD235313-1D7A-41AC-A3E0-A861A45A3B0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{261460A2-EF12-4960-8006-D29C98DD2962}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Date</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Cum P&amp;L</t>
   </si>
   <si>
     <t>MOMENTUM TRADER PRO  -  PERFORMANCE SUMMARY</t>
@@ -224,6 +227,33 @@
   </si>
   <si>
     <t xml:space="preserve">   - Profit Factor &gt; 1.5 = real edge.  Win rate alone means little.</t>
+  </si>
+  <si>
+    <t>● The equity curve is fully working. Cumulative P&amp;L computes correctly (₹905.88 after the win → ₹324.46 after the loss), and open/unfilled rows are skipped so the line stays clean. Test data was discarded — your journal is blank and ready.
+  ✅ Added: Equity Curve on the Summary sheet
+  - A line chart plotting your cumulative Net P&amp;L (after charges) trade-by-trade.
+  - X-axis = trade number, Y-axis = running total in ₹.
+  - It grows automatically as you log trades — no setup needed.
+  - Driven by a hidden Cum P&amp;L helper column (column T) so it doesn't clutter your journal.
+  - Rows without an Exit are skipped (not plotted as zero), so open trades don't create fake dips.
+  Your complete paper-trading kit
+  ┌─────────────────────────────────────┬────────────────────────────────────────────────────────┐
+  │                File                 │                        Purpose                         │
+  ├─────────────────────────────────────┼────────────────────────────────────────────────────────┤
+  │ momentum_trader_pro_v6.pine         │ The full strategy (arrows, ticket, filters, alerts)    │
+  ├─────────────────────────────────────┼────────────────────────────────────────────────────────┤
+  │ Momentum_Trader_Pro_Playbook.txt    │ Daily rules + notification setup                       │
+  ├─────────────────────────────────────┼────────────────────────────────────────────────────────┤
+  │ Momentum_Paper_Trading_Journal.xlsx │ Journal + live Win Rate / Profit Factor / Equity Curve │
+  └─────────────────────────────────────┴────────────────────────────────────────────────────────┘
+  How to read your equity curve
+  - Smooth line rising left-to-right = consistent edge. This is what you want.
+  - Big jagged swings = your position sizing or risk is too erratic.
+  - Rises then flattens/drops = the edge may be time-of-day or regime dependent — check your notes.
+  - Never recovers after a drawdown = stop and review before risking real money.
+  Log 30–50 trades and let the curve tell you the truth. If you want, once you've logged some real paper trades I can help you interpret the curve and stats and suggest which input (score threshold, ATR mult, stock selection) to adjust. Anything else
+  you want added to the kit?
+✻ Crunched for 3m 41s</t>
   </si>
 </sst>
 </file>
@@ -363,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -376,8 +406,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -390,6 +418,11 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,6 +459,526 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Equity Curve  -  Cumulative Net P&amp;L (Rs)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Journal!$T$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cum P&amp;L</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Journal!$T$2:$T$101</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3696-4190-A31B-2588AAD53D54}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1365221695"/>
+        <c:axId val="1365205375"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1365221695"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Trade number</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1365205375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1365205375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Cumulative Net P&amp;L (Rs)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1365221695"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="0"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77D8A6B7-86FF-979A-A5A5-83D67312E889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,8 +1297,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F008760D-F668-40C0-8C03-FE0018E687E6}">
-  <dimension ref="A1:S101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DCF53B-5850-4FC5-A075-5835F3D0A67D}">
+  <dimension ref="A1:T101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -765,9 +1318,10 @@
     <col min="16" max="17" width="6" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="30.7109375" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -825,8 +1379,11 @@
       <c r="S1" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -873,8 +1430,12 @@
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="7" t="e">
+        <f>IF(O2="",NA(),SUM($O$2:O2))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -921,8 +1482,12 @@
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3" s="7" t="e">
+        <f>IF(O3="",NA(),SUM($O$2:O3))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -969,8 +1534,12 @@
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="7" t="e">
+        <f>IF(O4="",NA(),SUM($O$2:O4))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1017,8 +1586,12 @@
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" s="7" t="e">
+        <f>IF(O5="",NA(),SUM($O$2:O5))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1065,8 +1638,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" s="7" t="e">
+        <f>IF(O6="",NA(),SUM($O$2:O6))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1113,8 +1690,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" s="7" t="e">
+        <f>IF(O7="",NA(),SUM($O$2:O7))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1161,8 +1742,12 @@
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="7" t="e">
+        <f>IF(O8="",NA(),SUM($O$2:O8))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1209,8 +1794,12 @@
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" s="7" t="e">
+        <f>IF(O9="",NA(),SUM($O$2:O9))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1257,8 +1846,12 @@
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T10" s="7" t="e">
+        <f>IF(O10="",NA(),SUM($O$2:O10))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1305,8 +1898,12 @@
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11" s="7" t="e">
+        <f>IF(O11="",NA(),SUM($O$2:O11))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1353,8 +1950,12 @@
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12" s="7" t="e">
+        <f>IF(O12="",NA(),SUM($O$2:O12))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1401,8 +2002,12 @@
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T13" s="7" t="e">
+        <f>IF(O13="",NA(),SUM($O$2:O13))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1449,8 +2054,12 @@
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14" s="7" t="e">
+        <f>IF(O14="",NA(),SUM($O$2:O14))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1497,8 +2106,12 @@
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" s="7" t="e">
+        <f>IF(O15="",NA(),SUM($O$2:O15))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1545,8 +2158,12 @@
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16" s="7" t="e">
+        <f>IF(O16="",NA(),SUM($O$2:O16))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1593,8 +2210,12 @@
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="7" t="e">
+        <f>IF(O17="",NA(),SUM($O$2:O17))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1641,8 +2262,12 @@
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="7" t="e">
+        <f>IF(O18="",NA(),SUM($O$2:O18))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1689,8 +2314,12 @@
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19" s="7" t="e">
+        <f>IF(O19="",NA(),SUM($O$2:O19))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1737,8 +2366,12 @@
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T20" s="7" t="e">
+        <f>IF(O20="",NA(),SUM($O$2:O20))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1785,8 +2418,12 @@
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21" s="7" t="e">
+        <f>IF(O21="",NA(),SUM($O$2:O21))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1833,8 +2470,12 @@
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22" s="7" t="e">
+        <f>IF(O22="",NA(),SUM($O$2:O22))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1881,8 +2522,12 @@
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" s="7" t="e">
+        <f>IF(O23="",NA(),SUM($O$2:O23))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1929,8 +2574,12 @@
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" s="7" t="e">
+        <f>IF(O24="",NA(),SUM($O$2:O24))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1977,8 +2626,12 @@
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T25" s="7" t="e">
+        <f>IF(O25="",NA(),SUM($O$2:O25))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2025,8 +2678,12 @@
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26" s="7" t="e">
+        <f>IF(O26="",NA(),SUM($O$2:O26))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2073,8 +2730,12 @@
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27" s="7" t="e">
+        <f>IF(O27="",NA(),SUM($O$2:O27))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2121,8 +2782,12 @@
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T28" s="7" t="e">
+        <f>IF(O28="",NA(),SUM($O$2:O28))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2169,8 +2834,12 @@
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29" s="7" t="e">
+        <f>IF(O29="",NA(),SUM($O$2:O29))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2217,8 +2886,12 @@
       </c>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30" s="7" t="e">
+        <f>IF(O30="",NA(),SUM($O$2:O30))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2265,8 +2938,12 @@
       </c>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T31" s="7" t="e">
+        <f>IF(O31="",NA(),SUM($O$2:O31))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2313,8 +2990,12 @@
       </c>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" s="7" t="e">
+        <f>IF(O32="",NA(),SUM($O$2:O32))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2361,8 +3042,12 @@
       </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" s="7" t="e">
+        <f>IF(O33="",NA(),SUM($O$2:O33))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2409,8 +3094,12 @@
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T34" s="7" t="e">
+        <f>IF(O34="",NA(),SUM($O$2:O34))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2457,8 +3146,12 @@
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35" s="7" t="e">
+        <f>IF(O35="",NA(),SUM($O$2:O35))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2505,8 +3198,12 @@
       </c>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T36" s="7" t="e">
+        <f>IF(O36="",NA(),SUM($O$2:O36))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2553,8 +3250,12 @@
       </c>
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T37" s="7" t="e">
+        <f>IF(O37="",NA(),SUM($O$2:O37))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2601,8 +3302,12 @@
       </c>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T38" s="7" t="e">
+        <f>IF(O38="",NA(),SUM($O$2:O38))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2649,8 +3354,12 @@
       </c>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T39" s="7" t="e">
+        <f>IF(O39="",NA(),SUM($O$2:O39))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2697,8 +3406,12 @@
       </c>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T40" s="7" t="e">
+        <f>IF(O40="",NA(),SUM($O$2:O40))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2745,8 +3458,12 @@
       </c>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41" s="7" t="e">
+        <f>IF(O41="",NA(),SUM($O$2:O41))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2793,8 +3510,12 @@
       </c>
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T42" s="7" t="e">
+        <f>IF(O42="",NA(),SUM($O$2:O42))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2841,8 +3562,12 @@
       </c>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T43" s="7" t="e">
+        <f>IF(O43="",NA(),SUM($O$2:O43))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2889,8 +3614,12 @@
       </c>
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T44" s="7" t="e">
+        <f>IF(O44="",NA(),SUM($O$2:O44))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2937,8 +3666,12 @@
       </c>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T45" s="7" t="e">
+        <f>IF(O45="",NA(),SUM($O$2:O45))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2985,8 +3718,12 @@
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T46" s="7" t="e">
+        <f>IF(O46="",NA(),SUM($O$2:O46))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -3033,8 +3770,12 @@
       </c>
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T47" s="7" t="e">
+        <f>IF(O47="",NA(),SUM($O$2:O47))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -3081,8 +3822,12 @@
       </c>
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T48" s="7" t="e">
+        <f>IF(O48="",NA(),SUM($O$2:O48))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3129,8 +3874,12 @@
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T49" s="7" t="e">
+        <f>IF(O49="",NA(),SUM($O$2:O49))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -3177,8 +3926,12 @@
       </c>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T50" s="7" t="e">
+        <f>IF(O50="",NA(),SUM($O$2:O50))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3225,8 +3978,12 @@
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T51" s="7" t="e">
+        <f>IF(O51="",NA(),SUM($O$2:O51))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3273,8 +4030,12 @@
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T52" s="7" t="e">
+        <f>IF(O52="",NA(),SUM($O$2:O52))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -3321,8 +4082,12 @@
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T53" s="7" t="e">
+        <f>IF(O53="",NA(),SUM($O$2:O53))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3369,8 +4134,12 @@
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T54" s="7" t="e">
+        <f>IF(O54="",NA(),SUM($O$2:O54))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3417,8 +4186,12 @@
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T55" s="7" t="e">
+        <f>IF(O55="",NA(),SUM($O$2:O55))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3465,8 +4238,12 @@
       </c>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T56" s="7" t="e">
+        <f>IF(O56="",NA(),SUM($O$2:O56))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3513,8 +4290,12 @@
       </c>
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T57" s="7" t="e">
+        <f>IF(O57="",NA(),SUM($O$2:O57))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3561,8 +4342,12 @@
       </c>
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T58" s="7" t="e">
+        <f>IF(O58="",NA(),SUM($O$2:O58))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3609,8 +4394,12 @@
       </c>
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T59" s="7" t="e">
+        <f>IF(O59="",NA(),SUM($O$2:O59))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3657,8 +4446,12 @@
       </c>
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T60" s="7" t="e">
+        <f>IF(O60="",NA(),SUM($O$2:O60))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3705,8 +4498,12 @@
       </c>
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T61" s="7" t="e">
+        <f>IF(O61="",NA(),SUM($O$2:O61))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3753,8 +4550,12 @@
       </c>
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T62" s="7" t="e">
+        <f>IF(O62="",NA(),SUM($O$2:O62))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3801,8 +4602,12 @@
       </c>
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T63" s="7" t="e">
+        <f>IF(O63="",NA(),SUM($O$2:O63))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3849,8 +4654,12 @@
       </c>
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T64" s="7" t="e">
+        <f>IF(O64="",NA(),SUM($O$2:O64))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3897,8 +4706,12 @@
       </c>
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T65" s="7" t="e">
+        <f>IF(O65="",NA(),SUM($O$2:O65))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3945,8 +4758,12 @@
       </c>
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T66" s="7" t="e">
+        <f>IF(O66="",NA(),SUM($O$2:O66))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3993,8 +4810,12 @@
       </c>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T67" s="7" t="e">
+        <f>IF(O67="",NA(),SUM($O$2:O67))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -4041,8 +4862,12 @@
       </c>
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T68" s="7" t="e">
+        <f>IF(O68="",NA(),SUM($O$2:O68))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -4089,8 +4914,12 @@
       </c>
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T69" s="7" t="e">
+        <f>IF(O69="",NA(),SUM($O$2:O69))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -4137,8 +4966,12 @@
       </c>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T70" s="7" t="e">
+        <f>IF(O70="",NA(),SUM($O$2:O70))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -4185,8 +5018,12 @@
       </c>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T71" s="7" t="e">
+        <f>IF(O71="",NA(),SUM($O$2:O71))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -4233,8 +5070,12 @@
       </c>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T72" s="7" t="e">
+        <f>IF(O72="",NA(),SUM($O$2:O72))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -4281,8 +5122,12 @@
       </c>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T73" s="7" t="e">
+        <f>IF(O73="",NA(),SUM($O$2:O73))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -4329,8 +5174,12 @@
       </c>
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T74" s="7" t="e">
+        <f>IF(O74="",NA(),SUM($O$2:O74))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -4377,8 +5226,12 @@
       </c>
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T75" s="7" t="e">
+        <f>IF(O75="",NA(),SUM($O$2:O75))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -4425,8 +5278,12 @@
       </c>
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T76" s="7" t="e">
+        <f>IF(O76="",NA(),SUM($O$2:O76))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -4473,8 +5330,12 @@
       </c>
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T77" s="7" t="e">
+        <f>IF(O77="",NA(),SUM($O$2:O77))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -4521,8 +5382,12 @@
       </c>
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T78" s="7" t="e">
+        <f>IF(O78="",NA(),SUM($O$2:O78))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -4569,8 +5434,12 @@
       </c>
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T79" s="7" t="e">
+        <f>IF(O79="",NA(),SUM($O$2:O79))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -4617,8 +5486,12 @@
       </c>
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T80" s="7" t="e">
+        <f>IF(O80="",NA(),SUM($O$2:O80))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -4665,8 +5538,12 @@
       </c>
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T81" s="7" t="e">
+        <f>IF(O81="",NA(),SUM($O$2:O81))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -4713,8 +5590,12 @@
       </c>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T82" s="7" t="e">
+        <f>IF(O82="",NA(),SUM($O$2:O82))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4761,8 +5642,12 @@
       </c>
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T83" s="7" t="e">
+        <f>IF(O83="",NA(),SUM($O$2:O83))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4809,8 +5694,12 @@
       </c>
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T84" s="7" t="e">
+        <f>IF(O84="",NA(),SUM($O$2:O84))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -4857,8 +5746,12 @@
       </c>
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T85" s="7" t="e">
+        <f>IF(O85="",NA(),SUM($O$2:O85))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -4905,8 +5798,12 @@
       </c>
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T86" s="7" t="e">
+        <f>IF(O86="",NA(),SUM($O$2:O86))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -4953,8 +5850,12 @@
       </c>
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T87" s="7" t="e">
+        <f>IF(O87="",NA(),SUM($O$2:O87))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -5001,8 +5902,12 @@
       </c>
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T88" s="7" t="e">
+        <f>IF(O88="",NA(),SUM($O$2:O88))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -5049,8 +5954,12 @@
       </c>
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T89" s="7" t="e">
+        <f>IF(O89="",NA(),SUM($O$2:O89))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -5097,8 +6006,12 @@
       </c>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T90" s="7" t="e">
+        <f>IF(O90="",NA(),SUM($O$2:O90))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -5145,8 +6058,12 @@
       </c>
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T91" s="7" t="e">
+        <f>IF(O91="",NA(),SUM($O$2:O91))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -5193,8 +6110,12 @@
       </c>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T92" s="7" t="e">
+        <f>IF(O92="",NA(),SUM($O$2:O92))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -5241,8 +6162,12 @@
       </c>
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T93" s="7" t="e">
+        <f>IF(O93="",NA(),SUM($O$2:O93))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -5289,8 +6214,12 @@
       </c>
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T94" s="7" t="e">
+        <f>IF(O94="",NA(),SUM($O$2:O94))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -5337,8 +6266,12 @@
       </c>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T95" s="7" t="e">
+        <f>IF(O95="",NA(),SUM($O$2:O95))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -5385,8 +6318,12 @@
       </c>
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T96" s="7" t="e">
+        <f>IF(O96="",NA(),SUM($O$2:O96))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -5433,8 +6370,12 @@
       </c>
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T97" s="7" t="e">
+        <f>IF(O97="",NA(),SUM($O$2:O97))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -5447,12 +6388,12 @@
         <v/>
       </c>
       <c r="I98" s="6" t="str">
-        <f t="shared" ref="I98:I129" si="27">IF(OR(H98="",G98=""),"",H98*G98)</f>
+        <f t="shared" ref="I98:I101" si="27">IF(OR(H98="",G98=""),"",H98*G98)</f>
         <v/>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="6" t="str">
-        <f t="shared" ref="K98:K129" si="28">IF(J98="","",IF(UPPER(C98)="BUY",D98*G98,J98*G98))</f>
+        <f t="shared" ref="K98:K101" si="28">IF(J98="","",IF(UPPER(C98)="BUY",D98*G98,J98*G98))</f>
         <v/>
       </c>
       <c r="L98" s="6" t="str">
@@ -5468,11 +6409,11 @@
         <v/>
       </c>
       <c r="O98" s="7" t="str">
-        <f t="shared" ref="O98:O129" si="29">IF(J98="","",M98-N98)</f>
+        <f t="shared" ref="O98:O101" si="29">IF(J98="","",M98-N98)</f>
         <v/>
       </c>
       <c r="P98" s="8" t="str">
-        <f t="shared" ref="P98:P129" si="30">IF(J98="","",IF(O98&gt;0,"WIN",IF(O98&lt;0,"LOSS","BE")))</f>
+        <f t="shared" ref="P98:P101" si="30">IF(J98="","",IF(O98&gt;0,"WIN",IF(O98&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
       <c r="Q98" s="5" t="str">
@@ -5481,8 +6422,12 @@
       </c>
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T98" s="7" t="e">
+        <f>IF(O98="",NA(),SUM($O$2:O98))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -5529,8 +6474,12 @@
       </c>
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T99" s="7" t="e">
+        <f>IF(O99="",NA(),SUM($O$2:O99))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -5577,8 +6526,12 @@
       </c>
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T100" s="7" t="e">
+        <f>IF(O100="",NA(),SUM($O$2:O100))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -5625,6 +6578,10 @@
       </c>
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
+      <c r="T101" s="7" t="e">
+        <f>IF(O101="",NA(),SUM($O$2:O101))</f>
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="P2:P101">
@@ -5636,7 +6593,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C101" xr:uid="{DFEE1921-5D71-4CAB-8768-24436D26B41A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C101" xr:uid="{58ED3A1D-6B85-4372-8CAA-6FE772C50DA3}">
       <formula1>"BUY,SELL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5645,7 +6602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64B54F8-3726-40CB-88AA-3F3BEAF64EBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493DDDCC-272E-4E09-8B87-9FD44795495D}">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5654,151 +6611,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="10"/>
+      <c r="A1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="11">
         <f>B3+B4+B5</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="11">
         <f>COUNTIF(Journal!P2:P101,"WIN")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="11">
         <f>COUNTIF(Journal!P2:P101,"LOSS")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="11">
         <f>COUNTIF(Journal!P2:P101,"BE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="17">
+      <c r="A6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="15">
         <f>IFERROR(B3/(B3+B4),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="12">
         <f>SUMIF(Journal!O2:O101,"&gt;0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="14">
+      <c r="A8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="12">
         <f>ABS(SUMIF(Journal!O2:O101,"&lt;0"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="19" t="str">
+      <c r="A9" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="17" t="str">
         <f>IFERROR(B7/B8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="21">
+      <c r="A10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="19">
         <f>SUM(Journal!O2:O101)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="14">
+      <c r="A11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12">
         <f>SUM(Journal!N2:N101)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="14">
+      <c r="A12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="12">
         <f>IFERROR(AVERAGEIF(Journal!O2:O101,"&gt;0"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="14">
+      <c r="A13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="12">
         <f>IFERROR(AVERAGEIF(Journal!O2:O101,"&lt;0"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="11">
         <f>IFERROR(B9/B2,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="13">
         <f>IFERROR(AVERAGE(Journal!Q2:Q101),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="A16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="11">
         <f>IFERROR(MAX(Journal!O2:O101),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="14">
+      <c r="A17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="12">
         <f>IFERROR(MIN(Journal!O2:O101),0)</f>
         <v>0</v>
       </c>
@@ -5807,8 +6764,8 @@
       <c r="B18" s="1"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>36</v>
+      <c r="A20" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -5816,135 +6773,141 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357A7C20-A481-41D3-89A6-9C55F49FBF09}">
-  <dimension ref="A1:A31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26BB404F-5F7C-46A9-92EC-718849F1BE64}">
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="95.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>37</v>
+      <c r="A1" s="21" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
